--- a/4_outputs/final/Table09.xlsx
+++ b/4_outputs/final/Table09.xlsx
@@ -417,13 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,17 +438,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Canonical</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Research-side distinctive terms</t>
+          <t>SWD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Policy-side distinctive terms</t>
+          <t>Chamfer</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Hausdorff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Gauss. W_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Grassmann</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>linear MMD</t>
         </is>
       </c>
     </row>
@@ -456,17 +480,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alleviation, china, approach, zakat, satellite, household, studies, indonesia, literature, relationship</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>social, cent, national, people, protection, services, population, vulnerable, living, million</t>
+          <t>0.509</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.684</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3.727</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.067</t>
         </is>
       </c>
     </row>
@@ -478,17 +522,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>crop, detection, plant, diseases, images, leaf, precision, techniques, soil, yield</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>population, food, children, prevalence, worst, access, hunger, million, births, ratio</t>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.454</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.618</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.629</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.057</t>
         </is>
       </c>
     </row>
@@ -500,17 +564,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>patients, cancer, cells, images, clinical, detection, disease, potential, genes, predict</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>health, services, care, national, population, births, mortality, rate, people, access</t>
+          <t>0.454</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.581</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3.717</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.129</t>
         </is>
       </c>
     </row>
@@ -522,17 +606,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cognitive, brain, neurons, sleep, agricultural, food, cells, motor, memory, poor</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>education, school, secondary, primary, national, quality, children, percent, access, vocational</t>
+          <t>0.399</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.487</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3.307</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.096</t>
         </is>
       </c>
     </row>
@@ -544,17 +648,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>menstrual, poor, pain, mothers, differences, relationship, patients, fertility, stress, sex</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gender, violence, equality, national, rights, girls, men, cent, sexual, domestic</t>
+          <t>0.429</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.529</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.646</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3.514</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.095</t>
         </is>
       </c>
     </row>
@@ -566,17 +690,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>irrigation, soil, agricultural, crop, salinity, agriculture, sup, potential, sub, yield</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sanitation, access, drinking, supply, national, wastewater, cent, services, population, clean</t>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.475</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.639</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3.598</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -588,17 +732,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.170</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>agricultural, poverty, agriculture, battery, optimization, approach, load, drying, poor, artificial</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>access, electricity, renewable, clean, worst best, population, affordable, index worst, cent, national</t>
+          <t>0.427</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.522</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.687</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3.729</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.105</t>
         </is>
       </c>
     </row>
@@ -610,17 +774,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>detection, image, food, recognition, leaf, plant, cnn, convolutional, disease, techniques</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>growth, employment, gdp, worst, labour, best, economic, cent, government, tourism</t>
+          <t>0.474</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.564</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3.566</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.065</t>
         </is>
       </c>
     </row>
@@ -632,17 +816,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.228</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>agricultural, agriculture, iot, detection, food, crop, plant, farming, farmers, soil</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>infrastructure, innovation, national, government, public, countries, strategy, access, population, intelligence</t>
+          <t>0.430</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.671</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.444</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.104</t>
         </is>
       </c>
     </row>
@@ -654,17 +858,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wealth, income inequality, effects, evidence, studies, que, distribution, literature, mobility, poor</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>people, rights, countries, migration, national, cent, disabilities, persons, discrimination, target</t>
+          <t>0.456</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.517</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.617</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.343</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.062</t>
         </is>
       </c>
     </row>
@@ -676,17 +900,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>detection, image, accident, traffic, object, poor, recognition, spatial, fusion, agricultural</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>housing, city, urban, transport, cities, public, waste, national, plan, green</t>
+          <t>0.446</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.542</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.677</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3.484</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.091</t>
         </is>
       </c>
     </row>
@@ -698,17 +942,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>food, agricultural, detection, quality, potential, behavior, samples, organic, design, compounds</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>waste, consumption, national, recycling, production, procurement, management, public, economy, circular</t>
+          <t>0.467</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.566</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.677</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3.462</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.094</t>
         </is>
       </c>
     </row>
@@ -720,17 +984,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>soil, agricultural, crop, moisture, drought, sub, rice, stress, agriculture, yield</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>climate, change, emissions, countries, national, action, global, energy, nations, united</t>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.498</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3.667</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.117</t>
         </is>
       </c>
     </row>
@@ -742,17 +1026,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>detection, images, aquaculture, food, bacterial, shrimp, cells, imaging, farming, techniques</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>marine, fish caught, biodiversity, rate, ocean, worst, population, sea, embodied, coastal</t>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.510</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3.753</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.098</t>
         </is>
       </c>
     </row>
@@ -764,17 +1068,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>soil, crop, agricultural, plant, spectral, images, sensing, detection, remote, field</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>biodiversity, forest, worst, national, protected, population, area, freshwater, species, best</t>
+          <t>0.394</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.464</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.578</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3.421</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.056</t>
         </is>
       </c>
     </row>
@@ -786,17 +1110,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>poor, food, covid-, pain, image, detection, social, studies, patients, brain</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>international, nations, peace, rights, united, security, human, law, world, global</t>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.520</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3.333</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.103</t>
         </is>
       </c>
     </row>
@@ -808,17 +1152,79 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sentiment, tweets, covid-, twitter, social, agricultural, dan, yang, zakat, media</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>countries, oecd, international, nations, united, agenda, report, financing, global, challenges</t>
+          <t>0.461</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.490</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.595</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.993</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ρ vs. canonical</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.485</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.444</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.243</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-0.243</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.620</t>
         </is>
       </c>
     </row>
